--- a/95 Файлы/Допуск. Дельта/Допуск. Дельта. Монтажлифтсервис.xlsx
+++ b/95 Файлы/Допуск. Дельта/Допуск. Дельта. Монтажлифтсервис.xlsx
@@ -224,7 +224,7 @@
     <t>Краснодарский край,г.Сочи, ул.Фадеева д.5, кв.31</t>
   </si>
   <si>
-    <t>с 01.04.2026 по 30.04.2026</t>
+    <t>с 01.05.2026 по 31.05.2026</t>
   </si>
 </sst>
 </file>
@@ -501,21 +501,78 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
@@ -527,63 +584,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -882,129 +882,129 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="29"/>
     </row>
     <row r="2" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="22"/>
+      <c r="C2" s="31"/>
       <c r="D2" s="7"/>
-      <c r="E2" s="42" t="s">
+      <c r="E2" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="43"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="33"/>
     </row>
     <row r="3" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="22"/>
+      <c r="C3" s="31"/>
       <c r="D3" s="7"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="25"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="35"/>
     </row>
     <row r="4" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="22"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="8"/>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="25"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="35"/>
     </row>
     <row r="5" spans="2:10" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="22"/>
+      <c r="C5" s="31"/>
       <c r="D5" s="9"/>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="27"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="46"/>
     </row>
     <row r="6" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="22"/>
+      <c r="C6" s="31"/>
       <c r="D6" s="9"/>
-      <c r="E6" s="28" t="s">
+      <c r="E6" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="29"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="48"/>
     </row>
     <row r="7" spans="2:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="22"/>
+      <c r="C7" s="31"/>
       <c r="D7" s="8"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="31"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="37"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="10"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="33"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="38"/>
     </row>
     <row r="9" spans="2:10" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="36"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="41"/>
     </row>
     <row r="10" spans="2:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="17" t="s">
@@ -1013,10 +1013,10 @@
       <c r="C10" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="D10" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="38"/>
+      <c r="E10" s="43"/>
       <c r="F10" s="17" t="s">
         <v>19</v>
       </c>
@@ -1026,10 +1026,10 @@
       <c r="H10" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="37" t="s">
+      <c r="I10" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="J10" s="38"/>
+      <c r="J10" s="43"/>
     </row>
     <row r="11" spans="2:10" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
@@ -1182,52 +1182,52 @@
       </c>
     </row>
     <row r="17" spans="2:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
     </row>
     <row r="18" spans="2:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="47" t="s">
+      <c r="B18" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
       <c r="F18" s="5"/>
       <c r="G18" s="15"/>
-      <c r="H18" s="48" t="s">
+      <c r="H18" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="I18" s="48"/>
-      <c r="J18" s="48"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B19" s="44" t="s">
+      <c r="B19" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
-      <c r="H19" s="32" t="s">
+      <c r="H19" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22"/>
     </row>
     <row r="20" spans="2:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="3">
         <f ca="1">TODAY()</f>
-        <v>46112</v>
+        <v>46140</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
@@ -1237,28 +1237,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="B17:J17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:J2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="E3:J3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="E5:J5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="E6:J6"/>
     <mergeCell ref="E7:J7"/>
     <mergeCell ref="E8:J8"/>
     <mergeCell ref="B9:J9"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="I10:J10"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="E5:J5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="E6:J6"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:J2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="E3:J3"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="B17:J17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="H18:J18"/>
   </mergeCells>
   <pageMargins left="0.31388888888888899" right="0.31388888888888899" top="0.55000000000000004" bottom="0.55000000000000004" header="0.31388888888888899" footer="0.31388888888888899"/>
   <pageSetup paperSize="9" scale="62" fitToHeight="0" orientation="portrait" r:id="rId1"/>
